--- a/evaluation/data/coordinators_responses.xlsx
+++ b/evaluation/data/coordinators_responses.xlsx
@@ -432,7 +432,7 @@
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>After exploring the application, do you consider the messaging function a useful tool for communicating with parents and the childcare tutors of the center?</t>
+          <t>After exploring the application, do you consider the messaging function a useful tool for communicating with parents and the childcare tutors of the child development center?</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -442,7 +442,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>What is your opinion of the usefulness of the children list, which lets you view the information of all the children at the center?</t>
+          <t>What is your opinion of the usefulness of the children list, which lets you view the information of all the children at the child development center?</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
